--- a/excel/02单元格格式与分列.xlsx
+++ b/excel/02单元格格式与分列.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3E22B3-312F-CA49-A2C3-A7353C77D030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56253E8E-6E8B-884E-A032-A2EBCC285EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="206">
   <si>
     <t>一、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -824,6 +824,34 @@
   </si>
   <si>
     <t>Excel在记录身份证长度数字时 默认只会存储15位精确度 导致后续数字展示为0</t>
+  </si>
+  <si>
+    <t>&lt;正数&gt;;&lt;负数&gt;;&lt;零&gt;;&lt;文本&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[蓝色]+0;[红色]-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[&gt;=60][蓝色]合格;[红色]不合格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0!.0,"万元" 或者 0\.0,"万元"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千分位符号（逗号）的右侧没有_"0"_或者_"#"_、_"?"_用以显示数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因此不显示千元以下的部分，再使用占位符!（叹号）或\（反斜杠）与句点结合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在千元前面显示句点本身而不是作为数值自身小数点使用，从而得到以“万元”为单位的显示效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1998,7 +2026,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:L54"/>
+  <dimension ref="A2:L62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2257,84 +2285,130 @@
       <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C36" s="132"/>
+      <c r="C36" s="132" t="s">
+        <v>199</v>
+      </c>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="A37" s="3" t="s">
+      <c r="C37" s="132" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C38" s="132" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C39" s="132"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C40" s="132" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C41" s="132" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C42" s="132" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C43" s="132" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C44" s="132"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="A45" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="3" customFormat="1" ht="14"/>
-    <row r="39" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B39" s="6" t="s">
+    <row r="46" spans="1:12" s="3" customFormat="1" ht="14"/>
+    <row r="47" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="B47" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L39" s="128"/>
-    </row>
-    <row r="40" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B40" s="6"/>
-      <c r="C40" s="132" t="s">
+      <c r="L47" s="128"/>
+    </row>
+    <row r="48" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="B48" s="6"/>
+      <c r="C48" s="132" t="s">
         <v>191</v>
       </c>
-      <c r="L40" s="128"/>
-    </row>
-    <row r="41" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B41" s="6"/>
-      <c r="C41" s="132" t="s">
+      <c r="L48" s="128"/>
+    </row>
+    <row r="49" spans="2:12" s="3" customFormat="1" ht="14">
+      <c r="B49" s="6"/>
+      <c r="C49" s="132" t="s">
         <v>168</v>
       </c>
-      <c r="L41" s="128"/>
-    </row>
-    <row r="42" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C42" s="6"/>
-    </row>
-    <row r="43" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B43" s="6" t="s">
+      <c r="L49" s="128"/>
+    </row>
+    <row r="50" spans="2:12" s="3" customFormat="1" ht="14">
+      <c r="C50" s="6"/>
+    </row>
+    <row r="51" spans="2:12" s="3" customFormat="1" ht="14">
+      <c r="B51" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="3" customFormat="1" ht="14"/>
-    <row r="45" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C45" s="6"/>
-    </row>
-    <row r="46" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C46" s="6"/>
-    </row>
-    <row r="47" spans="1:12" s="3" customFormat="1" ht="14"/>
-    <row r="48" spans="1:12">
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="3"/>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="3"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="3"/>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="3"/>
-      <c r="E54" s="3"/>
+    <row r="52" spans="2:12" s="3" customFormat="1" ht="14"/>
+    <row r="53" spans="2:12" s="3" customFormat="1" ht="14">
+      <c r="C53" s="6"/>
+    </row>
+    <row r="54" spans="2:12" s="3" customFormat="1" ht="14">
+      <c r="C54" s="6"/>
+    </row>
+    <row r="55" spans="2:12" s="3" customFormat="1" ht="14"/>
+    <row r="56" spans="2:12">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="2:12">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="2:12">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="2:12">
+      <c r="B59" s="3"/>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="2:12">
+      <c r="B60" s="3"/>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="2:12">
+      <c r="B61" s="3"/>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="2:12">
+      <c r="B62" s="3"/>
+      <c r="E62" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2953,7 +3027,7 @@
       </c>
       <c r="D24" s="67">
         <f t="shared" ref="D24:D32" ca="1" si="3">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2968,7 +3042,7 @@
       </c>
       <c r="D25" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2983,7 +3057,7 @@
       </c>
       <c r="D26" s="72">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2998,7 +3072,7 @@
       </c>
       <c r="D27" s="73">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3013,7 +3087,7 @@
       </c>
       <c r="D28" s="74">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3028,7 +3102,7 @@
       </c>
       <c r="D29" s="75">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3043,7 +3117,7 @@
       </c>
       <c r="D30" s="76">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3058,7 +3132,7 @@
       </c>
       <c r="D31" s="77">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3073,7 +3147,7 @@
       </c>
       <c r="D32" s="78">
         <f t="shared" ca="1" si="3"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3102,7 +3176,7 @@
       </c>
       <c r="D34" s="80">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3117,7 +3191,7 @@
       </c>
       <c r="D35" s="81">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3132,7 +3206,7 @@
       </c>
       <c r="D36" s="82">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3169,7 +3243,7 @@
       </c>
       <c r="D39" s="83">
         <f t="shared" ref="D39:D44" ca="1" si="4">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3184,7 +3258,7 @@
       </c>
       <c r="D40" s="84">
         <f t="shared" ca="1" si="4"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3199,7 +3273,7 @@
       </c>
       <c r="D41" s="85">
         <f t="shared" ca="1" si="4"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3214,7 +3288,7 @@
       </c>
       <c r="D42" s="86">
         <f t="shared" ca="1" si="4"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3229,7 +3303,7 @@
       </c>
       <c r="D43" s="87">
         <f t="shared" ca="1" si="4"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3244,7 +3318,7 @@
       </c>
       <c r="D44" s="88">
         <f t="shared" ca="1" si="4"/>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3301,7 +3375,7 @@
       </c>
       <c r="D48" s="96">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3386,7 +3460,7 @@
       </c>
       <c r="D54" s="108">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3401,7 +3475,7 @@
       </c>
       <c r="D55" s="109">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3416,7 +3490,7 @@
       </c>
       <c r="D56" s="110">
         <f ca="1">NOW()</f>
-        <v>46243.696555324073</v>
+        <v>46283.697333217591</v>
       </c>
     </row>
     <row r="57" spans="1:4">
